--- a/review-results/河北实时运行及市场出清数据-20260901.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260901.xlsx
@@ -1403,9 +1403,7 @@
       <s:c r="D2" s="12" t="n">
         <s:v>28733.9</s:v>
       </s:c>
-      <s:c r="E2" s="13" t="n">
-        <s:v>8469.79</s:v>
-      </s:c>
+      <s:c r="E2" s="13"/>
       <s:c r="F2" s="14" t="n">
         <s:v>1192.8</s:v>
       </s:c>
@@ -1431,9 +1429,7 @@
       <s:c r="D3" s="12" t="n">
         <s:v>28657.3</s:v>
       </s:c>
-      <s:c r="E3" s="13" t="n">
-        <s:v>8460.12</s:v>
-      </s:c>
+      <s:c r="E3" s="13"/>
       <s:c r="F3" s="14" t="n">
         <s:v>1030.1</s:v>
       </s:c>
@@ -1459,9 +1455,7 @@
       <s:c r="D4" s="12" t="n">
         <s:v>28454.4</s:v>
       </s:c>
-      <s:c r="E4" s="13" t="n">
-        <s:v>8449.43</s:v>
-      </s:c>
+      <s:c r="E4" s="13"/>
       <s:c r="F4" s="14" t="n">
         <s:v>890.6</s:v>
       </s:c>
@@ -1487,9 +1481,7 @@
       <s:c r="D5" s="12" t="n">
         <s:v>28386</s:v>
       </s:c>
-      <s:c r="E5" s="13" t="n">
-        <s:v>8440.84</s:v>
-      </s:c>
+      <s:c r="E5" s="13"/>
       <s:c r="F5" s="14" t="n">
         <s:v>784.6</s:v>
       </s:c>
@@ -1515,9 +1507,7 @@
       <s:c r="D6" s="12" t="n">
         <s:v>29340.5</s:v>
       </s:c>
-      <s:c r="E6" s="13" t="n">
-        <s:v>8426.8</s:v>
-      </s:c>
+      <s:c r="E6" s="13"/>
       <s:c r="F6" s="14" t="n">
         <s:v>706.1</s:v>
       </s:c>
@@ -1543,9 +1533,7 @@
       <s:c r="D7" s="12" t="n">
         <s:v>29041.5</s:v>
       </s:c>
-      <s:c r="E7" s="13" t="n">
-        <s:v>8419.35</s:v>
-      </s:c>
+      <s:c r="E7" s="13"/>
       <s:c r="F7" s="14" t="n">
         <s:v>645.4</s:v>
       </s:c>
@@ -1571,9 +1559,7 @@
       <s:c r="D8" s="12" t="n">
         <s:v>28975.6</s:v>
       </s:c>
-      <s:c r="E8" s="13" t="n">
-        <s:v>8413.73</s:v>
-      </s:c>
+      <s:c r="E8" s="13"/>
       <s:c r="F8" s="14" t="n">
         <s:v>572</s:v>
       </s:c>
@@ -1599,9 +1585,7 @@
       <s:c r="D9" s="12" t="n">
         <s:v>28575.7</s:v>
       </s:c>
-      <s:c r="E9" s="13" t="n">
-        <s:v>8406.17</s:v>
-      </s:c>
+      <s:c r="E9" s="13"/>
       <s:c r="F9" s="14" t="n">
         <s:v>518.1</s:v>
       </s:c>
@@ -1627,9 +1611,7 @@
       <s:c r="D10" s="12" t="n">
         <s:v>30675.2</s:v>
       </s:c>
-      <s:c r="E10" s="13" t="n">
-        <s:v>8398.01</s:v>
-      </s:c>
+      <s:c r="E10" s="13"/>
       <s:c r="F10" s="14" t="n">
         <s:v>493.6</s:v>
       </s:c>
@@ -1655,9 +1637,7 @@
       <s:c r="D11" s="12" t="n">
         <s:v>30603.5</s:v>
       </s:c>
-      <s:c r="E11" s="13" t="n">
-        <s:v>8391.42</s:v>
-      </s:c>
+      <s:c r="E11" s="13"/>
       <s:c r="F11" s="14" t="n">
         <s:v>480.4</s:v>
       </s:c>
@@ -1683,9 +1663,7 @@
       <s:c r="D12" s="12" t="n">
         <s:v>29623.7</s:v>
       </s:c>
-      <s:c r="E12" s="13" t="n">
-        <s:v>8385.28</s:v>
-      </s:c>
+      <s:c r="E12" s="13"/>
       <s:c r="F12" s="14" t="n">
         <s:v>472.2</s:v>
       </s:c>
@@ -1711,9 +1689,7 @@
       <s:c r="D13" s="12" t="n">
         <s:v>29597.5</s:v>
       </s:c>
-      <s:c r="E13" s="13" t="n">
-        <s:v>8378.5</s:v>
-      </s:c>
+      <s:c r="E13" s="13"/>
       <s:c r="F13" s="14" t="n">
         <s:v>482.1</s:v>
       </s:c>
@@ -1739,9 +1715,7 @@
       <s:c r="D14" s="12" t="n">
         <s:v>28805.1</s:v>
       </s:c>
-      <s:c r="E14" s="13" t="n">
-        <s:v>8375.54</s:v>
-      </s:c>
+      <s:c r="E14" s="13"/>
       <s:c r="F14" s="14" t="n">
         <s:v>503.1</s:v>
       </s:c>
@@ -1767,9 +1741,7 @@
       <s:c r="D15" s="12" t="n">
         <s:v>28541</s:v>
       </s:c>
-      <s:c r="E15" s="13" t="n">
-        <s:v>8369.61</s:v>
-      </s:c>
+      <s:c r="E15" s="13"/>
       <s:c r="F15" s="14" t="n">
         <s:v>507.7</s:v>
       </s:c>
@@ -1795,9 +1767,7 @@
       <s:c r="D16" s="12" t="n">
         <s:v>28403.3</s:v>
       </s:c>
-      <s:c r="E16" s="13" t="n">
-        <s:v>8364.54</s:v>
-      </s:c>
+      <s:c r="E16" s="13"/>
       <s:c r="F16" s="14" t="n">
         <s:v>521.2</s:v>
       </s:c>
@@ -1823,9 +1793,7 @@
       <s:c r="D17" s="12" t="n">
         <s:v>27788.1</s:v>
       </s:c>
-      <s:c r="E17" s="13" t="n">
-        <s:v>8359.05</s:v>
-      </s:c>
+      <s:c r="E17" s="13"/>
       <s:c r="F17" s="14" t="n">
         <s:v>543.6</s:v>
       </s:c>
@@ -1851,9 +1819,7 @@
       <s:c r="D18" s="12" t="n">
         <s:v>28123.9</s:v>
       </s:c>
-      <s:c r="E18" s="13" t="n">
-        <s:v>8365.55</s:v>
-      </s:c>
+      <s:c r="E18" s="13"/>
       <s:c r="F18" s="14" t="n">
         <s:v>576.7</s:v>
       </s:c>
@@ -1879,9 +1845,7 @@
       <s:c r="D19" s="12" t="n">
         <s:v>27779.9</s:v>
       </s:c>
-      <s:c r="E19" s="13" t="n">
-        <s:v>8363.3</s:v>
-      </s:c>
+      <s:c r="E19" s="13"/>
       <s:c r="F19" s="14" t="n">
         <s:v>599</s:v>
       </s:c>
@@ -1907,9 +1871,7 @@
       <s:c r="D20" s="12" t="n">
         <s:v>27846.3</s:v>
       </s:c>
-      <s:c r="E20" s="13" t="n">
-        <s:v>8361.97</s:v>
-      </s:c>
+      <s:c r="E20" s="13"/>
       <s:c r="F20" s="14" t="n">
         <s:v>609.1</s:v>
       </s:c>
@@ -1935,9 +1897,7 @@
       <s:c r="D21" s="12" t="n">
         <s:v>27881.6</s:v>
       </s:c>
-      <s:c r="E21" s="13" t="n">
-        <s:v>8357.21</s:v>
-      </s:c>
+      <s:c r="E21" s="13"/>
       <s:c r="F21" s="14" t="n">
         <s:v>620.1</s:v>
       </s:c>
@@ -1963,9 +1923,7 @@
       <s:c r="D22" s="12" t="n">
         <s:v>28190.5</s:v>
       </s:c>
-      <s:c r="E22" s="13" t="n">
-        <s:v>8357.01</s:v>
-      </s:c>
+      <s:c r="E22" s="13"/>
       <s:c r="F22" s="14" t="n">
         <s:v>644.6</s:v>
       </s:c>
@@ -1991,9 +1949,7 @@
       <s:c r="D23" s="12" t="n">
         <s:v>28339.2</s:v>
       </s:c>
-      <s:c r="E23" s="13" t="n">
-        <s:v>8358.02</s:v>
-      </s:c>
+      <s:c r="E23" s="13"/>
       <s:c r="F23" s="14" t="n">
         <s:v>672</s:v>
       </s:c>
@@ -2019,9 +1975,7 @@
       <s:c r="D24" s="12" t="n">
         <s:v>28465.3</s:v>
       </s:c>
-      <s:c r="E24" s="13" t="n">
-        <s:v>8365.3</s:v>
-      </s:c>
+      <s:c r="E24" s="13"/>
       <s:c r="F24" s="14" t="n">
         <s:v>707.9</s:v>
       </s:c>
@@ -2047,9 +2001,7 @@
       <s:c r="D25" s="12" t="n">
         <s:v>28793.8</s:v>
       </s:c>
-      <s:c r="E25" s="13" t="n">
-        <s:v>8367.16</s:v>
-      </s:c>
+      <s:c r="E25" s="13"/>
       <s:c r="F25" s="14" t="n">
         <s:v>808.7</s:v>
       </s:c>
@@ -2075,9 +2027,7 @@
       <s:c r="D26" s="12" t="n">
         <s:v>29071.7</s:v>
       </s:c>
-      <s:c r="E26" s="13" t="n">
-        <s:v>8143.12</s:v>
-      </s:c>
+      <s:c r="E26" s="13"/>
       <s:c r="F26" s="14" t="n">
         <s:v>1087.7</s:v>
       </s:c>
@@ -2103,9 +2053,7 @@
       <s:c r="D27" s="12" t="n">
         <s:v>29252.3</s:v>
       </s:c>
-      <s:c r="E27" s="13" t="n">
-        <s:v>7709.08</s:v>
-      </s:c>
+      <s:c r="E27" s="13"/>
       <s:c r="F27" s="14" t="n">
         <s:v>1513.4</s:v>
       </s:c>
@@ -2131,9 +2079,7 @@
       <s:c r="D28" s="12" t="n">
         <s:v>28805.5</s:v>
       </s:c>
-      <s:c r="E28" s="13" t="n">
-        <s:v>7025.75</s:v>
-      </s:c>
+      <s:c r="E28" s="13"/>
       <s:c r="F28" s="14" t="n">
         <s:v>2088.8</s:v>
       </s:c>
@@ -2159,9 +2105,7 @@
       <s:c r="D29" s="12" t="n">
         <s:v>27816.2</s:v>
       </s:c>
-      <s:c r="E29" s="13" t="n">
-        <s:v>6351.08</s:v>
-      </s:c>
+      <s:c r="E29" s="13"/>
       <s:c r="F29" s="14" t="n">
         <s:v>2782.1</s:v>
       </s:c>
@@ -2187,9 +2131,7 @@
       <s:c r="D30" s="12" t="n">
         <s:v>27817.5</s:v>
       </s:c>
-      <s:c r="E30" s="13" t="n">
-        <s:v>5887.63</s:v>
-      </s:c>
+      <s:c r="E30" s="13"/>
       <s:c r="F30" s="14" t="n">
         <s:v>3562.6</s:v>
       </s:c>
@@ -2215,9 +2157,7 @@
       <s:c r="D31" s="12" t="n">
         <s:v>26936.8</s:v>
       </s:c>
-      <s:c r="E31" s="13" t="n">
-        <s:v>5406.66</s:v>
-      </s:c>
+      <s:c r="E31" s="13"/>
       <s:c r="F31" s="14" t="n">
         <s:v>4414.3</s:v>
       </s:c>
@@ -2243,9 +2183,7 @@
       <s:c r="D32" s="12" t="n">
         <s:v>26372.2</s:v>
       </s:c>
-      <s:c r="E32" s="13" t="n">
-        <s:v>4946.22</s:v>
-      </s:c>
+      <s:c r="E32" s="13"/>
       <s:c r="F32" s="14" t="n">
         <s:v>5215.1</s:v>
       </s:c>
@@ -2271,9 +2209,7 @@
       <s:c r="D33" s="12" t="n">
         <s:v>26151.5</s:v>
       </s:c>
-      <s:c r="E33" s="13" t="n">
-        <s:v>4531.53</s:v>
-      </s:c>
+      <s:c r="E33" s="13"/>
       <s:c r="F33" s="14" t="n">
         <s:v>6123.1</s:v>
       </s:c>
@@ -2299,9 +2235,7 @@
       <s:c r="D34" s="12" t="n">
         <s:v>26160.2</s:v>
       </s:c>
-      <s:c r="E34" s="13" t="n">
-        <s:v>4184.9</s:v>
-      </s:c>
+      <s:c r="E34" s="13"/>
       <s:c r="F34" s="14" t="n">
         <s:v>6963.9</s:v>
       </s:c>
@@ -2327,9 +2261,7 @@
       <s:c r="D35" s="12" t="n">
         <s:v>26242.9</s:v>
       </s:c>
-      <s:c r="E35" s="13" t="n">
-        <s:v>4131.34</s:v>
-      </s:c>
+      <s:c r="E35" s="13"/>
       <s:c r="F35" s="14" t="n">
         <s:v>7687.5</s:v>
       </s:c>
@@ -2355,9 +2287,7 @@
       <s:c r="D36" s="12" t="n">
         <s:v>25697.8</s:v>
       </s:c>
-      <s:c r="E36" s="13" t="n">
-        <s:v>4165.76</s:v>
-      </s:c>
+      <s:c r="E36" s="13"/>
       <s:c r="F36" s="14" t="n">
         <s:v>8340.3</s:v>
       </s:c>
@@ -2383,9 +2313,7 @@
       <s:c r="D37" s="12" t="n">
         <s:v>25462.6</s:v>
       </s:c>
-      <s:c r="E37" s="13" t="n">
-        <s:v>4177.73</s:v>
-      </s:c>
+      <s:c r="E37" s="13"/>
       <s:c r="F37" s="14" t="n">
         <s:v>8896.2</s:v>
       </s:c>
@@ -2411,9 +2339,7 @@
       <s:c r="D38" s="12" t="n">
         <s:v>25112.7</s:v>
       </s:c>
-      <s:c r="E38" s="13" t="n">
-        <s:v>4202.95</s:v>
-      </s:c>
+      <s:c r="E38" s="13"/>
       <s:c r="F38" s="14" t="n">
         <s:v>9544.5</s:v>
       </s:c>
@@ -2439,9 +2365,7 @@
       <s:c r="D39" s="12" t="n">
         <s:v>24681.6</s:v>
       </s:c>
-      <s:c r="E39" s="13" t="n">
-        <s:v>4234.98</s:v>
-      </s:c>
+      <s:c r="E39" s="13"/>
       <s:c r="F39" s="14" t="n">
         <s:v>10010</s:v>
       </s:c>
@@ -2467,9 +2391,7 @@
       <s:c r="D40" s="12" t="n">
         <s:v>24691.5</s:v>
       </s:c>
-      <s:c r="E40" s="13" t="n">
-        <s:v>4276.17</s:v>
-      </s:c>
+      <s:c r="E40" s="13"/>
       <s:c r="F40" s="14" t="n">
         <s:v>9975.1</s:v>
       </s:c>
@@ -2495,9 +2417,7 @@
       <s:c r="D41" s="12" t="n">
         <s:v>24250</s:v>
       </s:c>
-      <s:c r="E41" s="13" t="n">
-        <s:v>4290.27</s:v>
-      </s:c>
+      <s:c r="E41" s="13"/>
       <s:c r="F41" s="14" t="n">
         <s:v>9576</s:v>
       </s:c>
@@ -2523,9 +2443,7 @@
       <s:c r="D42" s="12" t="n">
         <s:v>24420.1</s:v>
       </s:c>
-      <s:c r="E42" s="13" t="n">
-        <s:v>4314.45</s:v>
-      </s:c>
+      <s:c r="E42" s="13"/>
       <s:c r="F42" s="14" t="n">
         <s:v>9731.3</s:v>
       </s:c>
@@ -2551,9 +2469,7 @@
       <s:c r="D43" s="12" t="n">
         <s:v>24473.7</s:v>
       </s:c>
-      <s:c r="E43" s="13" t="n">
-        <s:v>4331.38</s:v>
-      </s:c>
+      <s:c r="E43" s="13"/>
       <s:c r="F43" s="14" t="n">
         <s:v>9730.7</s:v>
       </s:c>
@@ -2579,9 +2495,7 @@
       <s:c r="D44" s="12" t="n">
         <s:v>24508.9</s:v>
       </s:c>
-      <s:c r="E44" s="13" t="n">
-        <s:v>4357.8</s:v>
-      </s:c>
+      <s:c r="E44" s="13"/>
       <s:c r="F44" s="14" t="n">
         <s:v>10032.9</s:v>
       </s:c>
@@ -2607,9 +2521,7 @@
       <s:c r="D45" s="12" t="n">
         <s:v>24564</s:v>
       </s:c>
-      <s:c r="E45" s="13" t="n">
-        <s:v>4366.63</s:v>
-      </s:c>
+      <s:c r="E45" s="13"/>
       <s:c r="F45" s="14" t="n">
         <s:v>10375.8</s:v>
       </s:c>
@@ -2635,9 +2547,7 @@
       <s:c r="D46" s="12" t="n">
         <s:v>26246.1</s:v>
       </s:c>
-      <s:c r="E46" s="13" t="n">
-        <s:v>4395.82</s:v>
-      </s:c>
+      <s:c r="E46" s="13"/>
       <s:c r="F46" s="14" t="n">
         <s:v>11671.6</s:v>
       </s:c>
@@ -2663,9 +2573,7 @@
       <s:c r="D47" s="12" t="n">
         <s:v>26175.9</s:v>
       </s:c>
-      <s:c r="E47" s="13" t="n">
-        <s:v>4415.28</s:v>
-      </s:c>
+      <s:c r="E47" s="13"/>
       <s:c r="F47" s="14" t="n">
         <s:v>12057</s:v>
       </s:c>
@@ -2691,9 +2599,7 @@
       <s:c r="D48" s="12" t="n">
         <s:v>25690</s:v>
       </s:c>
-      <s:c r="E48" s="13" t="n">
-        <s:v>4412.62</s:v>
-      </s:c>
+      <s:c r="E48" s="13"/>
       <s:c r="F48" s="14" t="n">
         <s:v>11888.8</s:v>
       </s:c>
@@ -2719,9 +2625,7 @@
       <s:c r="D49" s="12" t="n">
         <s:v>24471.3</s:v>
       </s:c>
-      <s:c r="E49" s="13" t="n">
-        <s:v>4366.12</s:v>
-      </s:c>
+      <s:c r="E49" s="13"/>
       <s:c r="F49" s="14" t="n">
         <s:v>11652.3</s:v>
       </s:c>
@@ -2747,9 +2651,7 @@
       <s:c r="D50" s="12" t="n">
         <s:v>24840.2</s:v>
       </s:c>
-      <s:c r="E50" s="13" t="n">
-        <s:v>4371.46</s:v>
-      </s:c>
+      <s:c r="E50" s="13"/>
       <s:c r="F50" s="14" t="n">
         <s:v>11960.3</s:v>
       </s:c>
@@ -2775,9 +2677,7 @@
       <s:c r="D51" s="12" t="n">
         <s:v>24879.7</s:v>
       </s:c>
-      <s:c r="E51" s="13" t="n">
-        <s:v>4352.78</s:v>
-      </s:c>
+      <s:c r="E51" s="13"/>
       <s:c r="F51" s="14" t="n">
         <s:v>11944.1</s:v>
       </s:c>
@@ -2803,9 +2703,7 @@
       <s:c r="D52" s="12" t="n">
         <s:v>24570.9</s:v>
       </s:c>
-      <s:c r="E52" s="13" t="n">
-        <s:v>4368.49</s:v>
-      </s:c>
+      <s:c r="E52" s="13"/>
       <s:c r="F52" s="14" t="n">
         <s:v>11794.5</s:v>
       </s:c>
@@ -2831,9 +2729,7 @@
       <s:c r="D53" s="12" t="n">
         <s:v>24892.6</s:v>
       </s:c>
-      <s:c r="E53" s="13" t="n">
-        <s:v>4367.9</s:v>
-      </s:c>
+      <s:c r="E53" s="13"/>
       <s:c r="F53" s="14" t="n">
         <s:v>11860.1</s:v>
       </s:c>
@@ -2859,9 +2755,7 @@
       <s:c r="D54" s="12" t="n">
         <s:v>25109.4</s:v>
       </s:c>
-      <s:c r="E54" s="13" t="n">
-        <s:v>4358.7</s:v>
-      </s:c>
+      <s:c r="E54" s="13"/>
       <s:c r="F54" s="14" t="n">
         <s:v>11686.3</s:v>
       </s:c>
@@ -2887,9 +2781,7 @@
       <s:c r="D55" s="12" t="n">
         <s:v>25250.3</s:v>
       </s:c>
-      <s:c r="E55" s="13" t="n">
-        <s:v>4359.53</s:v>
-      </s:c>
+      <s:c r="E55" s="13"/>
       <s:c r="F55" s="14" t="n">
         <s:v>11769.1</s:v>
       </s:c>
@@ -2915,9 +2807,7 @@
       <s:c r="D56" s="12" t="n">
         <s:v>25482.2</s:v>
       </s:c>
-      <s:c r="E56" s="13" t="n">
-        <s:v>4355.94</s:v>
-      </s:c>
+      <s:c r="E56" s="13"/>
       <s:c r="F56" s="14" t="n">
         <s:v>11575.1</s:v>
       </s:c>
@@ -2943,9 +2833,7 @@
       <s:c r="D57" s="12" t="n">
         <s:v>25398.3</s:v>
       </s:c>
-      <s:c r="E57" s="13" t="n">
-        <s:v>4347.6</s:v>
-      </s:c>
+      <s:c r="E57" s="13"/>
       <s:c r="F57" s="14" t="n">
         <s:v>11174.3</s:v>
       </s:c>
@@ -2971,9 +2859,7 @@
       <s:c r="D58" s="12" t="n">
         <s:v>26034.9</s:v>
       </s:c>
-      <s:c r="E58" s="13" t="n">
-        <s:v>4334.79</s:v>
-      </s:c>
+      <s:c r="E58" s="13"/>
       <s:c r="F58" s="14" t="n">
         <s:v>10849.8</s:v>
       </s:c>
@@ -2999,9 +2885,7 @@
       <s:c r="D59" s="12" t="n">
         <s:v>26256.7</s:v>
       </s:c>
-      <s:c r="E59" s="13" t="n">
-        <s:v>4351.18</s:v>
-      </s:c>
+      <s:c r="E59" s="13"/>
       <s:c r="F59" s="14" t="n">
         <s:v>10296.7</s:v>
       </s:c>
@@ -3027,9 +2911,7 @@
       <s:c r="D60" s="12" t="n">
         <s:v>26676.4</s:v>
       </s:c>
-      <s:c r="E60" s="13" t="n">
-        <s:v>4345.68</s:v>
-      </s:c>
+      <s:c r="E60" s="13"/>
       <s:c r="F60" s="14" t="n">
         <s:v>10124.5</s:v>
       </s:c>
@@ -3055,9 +2937,7 @@
       <s:c r="D61" s="12" t="n">
         <s:v>26870.1</s:v>
       </s:c>
-      <s:c r="E61" s="13" t="n">
-        <s:v>4322.28</s:v>
-      </s:c>
+      <s:c r="E61" s="13"/>
       <s:c r="F61" s="14" t="n">
         <s:v>9826.4</s:v>
       </s:c>
@@ -3083,9 +2963,7 @@
       <s:c r="D62" s="12" t="n">
         <s:v>27201.4</s:v>
       </s:c>
-      <s:c r="E62" s="13" t="n">
-        <s:v>4401.33</s:v>
-      </s:c>
+      <s:c r="E62" s="13"/>
       <s:c r="F62" s="14" t="n">
         <s:v>9305.7</s:v>
       </s:c>
@@ -3111,9 +2989,7 @@
       <s:c r="D63" s="12" t="n">
         <s:v>28113.2</s:v>
       </s:c>
-      <s:c r="E63" s="13" t="n">
-        <s:v>4782.72</s:v>
-      </s:c>
+      <s:c r="E63" s="13"/>
       <s:c r="F63" s="14" t="n">
         <s:v>8861.9</s:v>
       </s:c>
@@ -3139,9 +3015,7 @@
       <s:c r="D64" s="12" t="n">
         <s:v>28504.6</s:v>
       </s:c>
-      <s:c r="E64" s="13" t="n">
-        <s:v>5207.14</s:v>
-      </s:c>
+      <s:c r="E64" s="13"/>
       <s:c r="F64" s="14" t="n">
         <s:v>8324.8</s:v>
       </s:c>
@@ -3167,9 +3041,7 @@
       <s:c r="D65" s="12" t="n">
         <s:v>28968.9</s:v>
       </s:c>
-      <s:c r="E65" s="13" t="n">
-        <s:v>5878.63</s:v>
-      </s:c>
+      <s:c r="E65" s="13"/>
       <s:c r="F65" s="14" t="n">
         <s:v>7522.3</s:v>
       </s:c>
@@ -3195,9 +3067,7 @@
       <s:c r="D66" s="12" t="n">
         <s:v>29785.8</s:v>
       </s:c>
-      <s:c r="E66" s="13" t="n">
-        <s:v>6546.52</s:v>
-      </s:c>
+      <s:c r="E66" s="13"/>
       <s:c r="F66" s="14" t="n">
         <s:v>6763</s:v>
       </s:c>
@@ -3223,9 +3093,7 @@
       <s:c r="D67" s="12" t="n">
         <s:v>30720.8</s:v>
       </s:c>
-      <s:c r="E67" s="13" t="n">
-        <s:v>7010.45</s:v>
-      </s:c>
+      <s:c r="E67" s="13"/>
       <s:c r="F67" s="14" t="n">
         <s:v>6057.9</s:v>
       </s:c>
@@ -3251,9 +3119,7 @@
       <s:c r="D68" s="12" t="n">
         <s:v>31812.4</s:v>
       </s:c>
-      <s:c r="E68" s="13" t="n">
-        <s:v>7476.59</s:v>
-      </s:c>
+      <s:c r="E68" s="13"/>
       <s:c r="F68" s="14" t="n">
         <s:v>5197</s:v>
       </s:c>
@@ -3279,9 +3145,7 @@
       <s:c r="D69" s="12" t="n">
         <s:v>33027.1</s:v>
       </s:c>
-      <s:c r="E69" s="13" t="n">
-        <s:v>7938.2</s:v>
-      </s:c>
+      <s:c r="E69" s="13"/>
       <s:c r="F69" s="14" t="n">
         <s:v>4343.4</s:v>
       </s:c>
@@ -3307,9 +3171,7 @@
       <s:c r="D70" s="12" t="n">
         <s:v>34254.8</s:v>
       </s:c>
-      <s:c r="E70" s="13" t="n">
-        <s:v>8352.44</s:v>
-      </s:c>
+      <s:c r="E70" s="13"/>
       <s:c r="F70" s="14" t="n">
         <s:v>3465.1</s:v>
       </s:c>
@@ -3335,9 +3197,7 @@
       <s:c r="D71" s="12" t="n">
         <s:v>34931.5</s:v>
       </s:c>
-      <s:c r="E71" s="13" t="n">
-        <s:v>8562.01</s:v>
-      </s:c>
+      <s:c r="E71" s="13"/>
       <s:c r="F71" s="14" t="n">
         <s:v>2602.5</s:v>
       </s:c>
@@ -3363,9 +3223,7 @@
       <s:c r="D72" s="12" t="n">
         <s:v>35486.6</s:v>
       </s:c>
-      <s:c r="E72" s="13" t="n">
-        <s:v>8529.58</s:v>
-      </s:c>
+      <s:c r="E72" s="13"/>
       <s:c r="F72" s="14" t="n">
         <s:v>1868.6</s:v>
       </s:c>
@@ -3391,9 +3249,7 @@
       <s:c r="D73" s="12" t="n">
         <s:v>36088.2</s:v>
       </s:c>
-      <s:c r="E73" s="13" t="n">
-        <s:v>8502.06</s:v>
-      </s:c>
+      <s:c r="E73" s="13"/>
       <s:c r="F73" s="14" t="n">
         <s:v>1314.2</s:v>
       </s:c>
@@ -3419,9 +3275,7 @@
       <s:c r="D74" s="12" t="n">
         <s:v>35760.2</s:v>
       </s:c>
-      <s:c r="E74" s="13" t="n">
-        <s:v>8486.29</s:v>
-      </s:c>
+      <s:c r="E74" s="13"/>
       <s:c r="F74" s="14" t="n">
         <s:v>923.7</s:v>
       </s:c>
@@ -3447,9 +3301,7 @@
       <s:c r="D75" s="12" t="n">
         <s:v>36061.8</s:v>
       </s:c>
-      <s:c r="E75" s="13" t="n">
-        <s:v>8473.31</s:v>
-      </s:c>
+      <s:c r="E75" s="13"/>
       <s:c r="F75" s="14" t="n">
         <s:v>706.2</s:v>
       </s:c>
@@ -3475,9 +3327,7 @@
       <s:c r="D76" s="12" t="n">
         <s:v>36125.6</s:v>
       </s:c>
-      <s:c r="E76" s="13" t="n">
-        <s:v>8470.44</s:v>
-      </s:c>
+      <s:c r="E76" s="13"/>
       <s:c r="F76" s="14" t="n">
         <s:v>614.8</s:v>
       </s:c>
@@ -3503,9 +3353,7 @@
       <s:c r="D77" s="12" t="n">
         <s:v>36064.3</s:v>
       </s:c>
-      <s:c r="E77" s="13" t="n">
-        <s:v>8466.12</s:v>
-      </s:c>
+      <s:c r="E77" s="13"/>
       <s:c r="F77" s="14" t="n">
         <s:v>695.3</s:v>
       </s:c>
@@ -3531,9 +3379,7 @@
       <s:c r="D78" s="12" t="n">
         <s:v>36030.9</s:v>
       </s:c>
-      <s:c r="E78" s="13" t="n">
-        <s:v>8467.18</s:v>
-      </s:c>
+      <s:c r="E78" s="13"/>
       <s:c r="F78" s="14" t="n">
         <s:v>788.1</s:v>
       </s:c>
@@ -3559,9 +3405,7 @@
       <s:c r="D79" s="12" t="n">
         <s:v>35727.2</s:v>
       </s:c>
-      <s:c r="E79" s="13" t="n">
-        <s:v>8475.75</s:v>
-      </s:c>
+      <s:c r="E79" s="13"/>
       <s:c r="F79" s="14" t="n">
         <s:v>926.5</s:v>
       </s:c>
@@ -3587,9 +3431,7 @@
       <s:c r="D80" s="12" t="n">
         <s:v>35227.6</s:v>
       </s:c>
-      <s:c r="E80" s="13" t="n">
-        <s:v>8484.97</s:v>
-      </s:c>
+      <s:c r="E80" s="13"/>
       <s:c r="F80" s="14" t="n">
         <s:v>1076.7</s:v>
       </s:c>
@@ -3615,9 +3457,7 @@
       <s:c r="D81" s="12" t="n">
         <s:v>34536.7</s:v>
       </s:c>
-      <s:c r="E81" s="13" t="n">
-        <s:v>8492.42</s:v>
-      </s:c>
+      <s:c r="E81" s="13"/>
       <s:c r="F81" s="14" t="n">
         <s:v>1171.7</s:v>
       </s:c>
@@ -3643,9 +3483,7 @@
       <s:c r="D82" s="12" t="n">
         <s:v>34543.9</s:v>
       </s:c>
-      <s:c r="E82" s="13" t="n">
-        <s:v>8494.38</s:v>
-      </s:c>
+      <s:c r="E82" s="13"/>
       <s:c r="F82" s="14" t="n">
         <s:v>1282.6</s:v>
       </s:c>
@@ -3671,9 +3509,7 @@
       <s:c r="D83" s="12" t="n">
         <s:v>34088.9</s:v>
       </s:c>
-      <s:c r="E83" s="13" t="n">
-        <s:v>8496.36</s:v>
-      </s:c>
+      <s:c r="E83" s="13"/>
       <s:c r="F83" s="14" t="n">
         <s:v>1333.8</s:v>
       </s:c>
@@ -3699,9 +3535,7 @@
       <s:c r="D84" s="12" t="n">
         <s:v>33923.7</s:v>
       </s:c>
-      <s:c r="E84" s="13" t="n">
-        <s:v>8495.71</s:v>
-      </s:c>
+      <s:c r="E84" s="13"/>
       <s:c r="F84" s="14" t="n">
         <s:v>1377.8</s:v>
       </s:c>
@@ -3727,9 +3561,7 @@
       <s:c r="D85" s="12" t="n">
         <s:v>33451.3</s:v>
       </s:c>
-      <s:c r="E85" s="13" t="n">
-        <s:v>8496.39</s:v>
-      </s:c>
+      <s:c r="E85" s="13"/>
       <s:c r="F85" s="14" t="n">
         <s:v>1445.1</s:v>
       </s:c>
@@ -3755,9 +3587,7 @@
       <s:c r="D86" s="12" t="n">
         <s:v>33342.4</s:v>
       </s:c>
-      <s:c r="E86" s="13" t="n">
-        <s:v>8477.68</s:v>
-      </s:c>
+      <s:c r="E86" s="13"/>
       <s:c r="F86" s="14" t="n">
         <s:v>1490.5</s:v>
       </s:c>
@@ -3783,9 +3613,7 @@
       <s:c r="D87" s="12" t="n">
         <s:v>32902.6</s:v>
       </s:c>
-      <s:c r="E87" s="13" t="n">
-        <s:v>8474.29</s:v>
-      </s:c>
+      <s:c r="E87" s="13"/>
       <s:c r="F87" s="14" t="n">
         <s:v>1549.6</s:v>
       </s:c>
@@ -3811,9 +3639,7 @@
       <s:c r="D88" s="12" t="n">
         <s:v>32520</s:v>
       </s:c>
-      <s:c r="E88" s="13" t="n">
-        <s:v>8471.38</s:v>
-      </s:c>
+      <s:c r="E88" s="13"/>
       <s:c r="F88" s="14" t="n">
         <s:v>1594.6</s:v>
       </s:c>
@@ -3839,9 +3665,7 @@
       <s:c r="D89" s="12" t="n">
         <s:v>32117.7</s:v>
       </s:c>
-      <s:c r="E89" s="13" t="n">
-        <s:v>8469.46</s:v>
-      </s:c>
+      <s:c r="E89" s="13"/>
       <s:c r="F89" s="14" t="n">
         <s:v>1662.5</s:v>
       </s:c>
@@ -3867,9 +3691,7 @@
       <s:c r="D90" s="12" t="n">
         <s:v>31796.7</s:v>
       </s:c>
-      <s:c r="E90" s="13" t="n">
-        <s:v>8414.59</s:v>
-      </s:c>
+      <s:c r="E90" s="13"/>
       <s:c r="F90" s="14" t="n">
         <s:v>1709</s:v>
       </s:c>
@@ -3895,9 +3717,7 @@
       <s:c r="D91" s="12" t="n">
         <s:v>31317.1</s:v>
       </s:c>
-      <s:c r="E91" s="13" t="n">
-        <s:v>8405.87</s:v>
-      </s:c>
+      <s:c r="E91" s="13"/>
       <s:c r="F91" s="14" t="n">
         <s:v>1706.9</s:v>
       </s:c>
@@ -3923,9 +3743,7 @@
       <s:c r="D92" s="12" t="n">
         <s:v>30612.5</s:v>
       </s:c>
-      <s:c r="E92" s="13" t="n">
-        <s:v>8400.52</s:v>
-      </s:c>
+      <s:c r="E92" s="13"/>
       <s:c r="F92" s="14" t="n">
         <s:v>1812.6</s:v>
       </s:c>
@@ -3951,9 +3769,7 @@
       <s:c r="D93" s="12" t="n">
         <s:v>30284.8</s:v>
       </s:c>
-      <s:c r="E93" s="13" t="n">
-        <s:v>8393.72</s:v>
-      </s:c>
+      <s:c r="E93" s="13"/>
       <s:c r="F93" s="14" t="n">
         <s:v>1857</s:v>
       </s:c>
@@ -3979,9 +3795,7 @@
       <s:c r="D94" s="12" t="n">
         <s:v>29722.3</s:v>
       </s:c>
-      <s:c r="E94" s="13" t="n">
-        <s:v>8386.32</s:v>
-      </s:c>
+      <s:c r="E94" s="13"/>
       <s:c r="F94" s="14" t="n">
         <s:v>1920.8</s:v>
       </s:c>
@@ -4007,9 +3821,7 @@
       <s:c r="D95" s="12" t="n">
         <s:v>29172.8</s:v>
       </s:c>
-      <s:c r="E95" s="13" t="n">
-        <s:v>8375.86</s:v>
-      </s:c>
+      <s:c r="E95" s="13"/>
       <s:c r="F95" s="14" t="n">
         <s:v>1969.1</s:v>
       </s:c>
@@ -4035,9 +3847,7 @@
       <s:c r="D96" s="12" t="n">
         <s:v>28328.4</s:v>
       </s:c>
-      <s:c r="E96" s="13" t="n">
-        <s:v>8365.49</s:v>
-      </s:c>
+      <s:c r="E96" s="13"/>
       <s:c r="F96" s="14" t="n">
         <s:v>2077.6</s:v>
       </s:c>
@@ -4065,9 +3875,7 @@
       <s:c r="D97" s="12" t="n">
         <s:v>28728.1</s:v>
       </s:c>
-      <s:c r="E97" s="13" t="n">
-        <s:v>8354.02</s:v>
-      </s:c>
+      <s:c r="E97" s="13"/>
       <s:c r="F97" s="14" t="n">
         <s:v>2164.7</s:v>
       </s:c>

--- a/review-results/河北实时运行及市场出清数据-20260901.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260901.xlsx
@@ -1403,7 +1403,9 @@
       <s:c r="D2" s="12" t="n">
         <s:v>28733.9</s:v>
       </s:c>
-      <s:c r="E2" s="13"/>
+      <s:c r="E2" s="13" t="n">
+        <s:v>8469.79</s:v>
+      </s:c>
       <s:c r="F2" s="14" t="n">
         <s:v>1192.8</s:v>
       </s:c>
@@ -1429,7 +1431,9 @@
       <s:c r="D3" s="12" t="n">
         <s:v>28657.3</s:v>
       </s:c>
-      <s:c r="E3" s="13"/>
+      <s:c r="E3" s="13" t="n">
+        <s:v>8460.12</s:v>
+      </s:c>
       <s:c r="F3" s="14" t="n">
         <s:v>1030.1</s:v>
       </s:c>
@@ -1455,7 +1459,9 @@
       <s:c r="D4" s="12" t="n">
         <s:v>28454.4</s:v>
       </s:c>
-      <s:c r="E4" s="13"/>
+      <s:c r="E4" s="13" t="n">
+        <s:v>8449.43</s:v>
+      </s:c>
       <s:c r="F4" s="14" t="n">
         <s:v>890.6</s:v>
       </s:c>
@@ -1481,7 +1487,9 @@
       <s:c r="D5" s="12" t="n">
         <s:v>28386</s:v>
       </s:c>
-      <s:c r="E5" s="13"/>
+      <s:c r="E5" s="13" t="n">
+        <s:v>8440.84</s:v>
+      </s:c>
       <s:c r="F5" s="14" t="n">
         <s:v>784.6</s:v>
       </s:c>
@@ -1507,7 +1515,9 @@
       <s:c r="D6" s="12" t="n">
         <s:v>29340.5</s:v>
       </s:c>
-      <s:c r="E6" s="13"/>
+      <s:c r="E6" s="13" t="n">
+        <s:v>8426.8</s:v>
+      </s:c>
       <s:c r="F6" s="14" t="n">
         <s:v>706.1</s:v>
       </s:c>
@@ -1533,7 +1543,9 @@
       <s:c r="D7" s="12" t="n">
         <s:v>29041.5</s:v>
       </s:c>
-      <s:c r="E7" s="13"/>
+      <s:c r="E7" s="13" t="n">
+        <s:v>8419.35</s:v>
+      </s:c>
       <s:c r="F7" s="14" t="n">
         <s:v>645.4</s:v>
       </s:c>
@@ -1559,7 +1571,9 @@
       <s:c r="D8" s="12" t="n">
         <s:v>28975.6</s:v>
       </s:c>
-      <s:c r="E8" s="13"/>
+      <s:c r="E8" s="13" t="n">
+        <s:v>8413.73</s:v>
+      </s:c>
       <s:c r="F8" s="14" t="n">
         <s:v>572</s:v>
       </s:c>
@@ -1585,7 +1599,9 @@
       <s:c r="D9" s="12" t="n">
         <s:v>28575.7</s:v>
       </s:c>
-      <s:c r="E9" s="13"/>
+      <s:c r="E9" s="13" t="n">
+        <s:v>8406.17</s:v>
+      </s:c>
       <s:c r="F9" s="14" t="n">
         <s:v>518.1</s:v>
       </s:c>
@@ -1611,7 +1627,9 @@
       <s:c r="D10" s="12" t="n">
         <s:v>30675.2</s:v>
       </s:c>
-      <s:c r="E10" s="13"/>
+      <s:c r="E10" s="13" t="n">
+        <s:v>8398.01</s:v>
+      </s:c>
       <s:c r="F10" s="14" t="n">
         <s:v>493.6</s:v>
       </s:c>
@@ -1637,7 +1655,9 @@
       <s:c r="D11" s="12" t="n">
         <s:v>30603.5</s:v>
       </s:c>
-      <s:c r="E11" s="13"/>
+      <s:c r="E11" s="13" t="n">
+        <s:v>8391.42</s:v>
+      </s:c>
       <s:c r="F11" s="14" t="n">
         <s:v>480.4</s:v>
       </s:c>
@@ -1663,7 +1683,9 @@
       <s:c r="D12" s="12" t="n">
         <s:v>29623.7</s:v>
       </s:c>
-      <s:c r="E12" s="13"/>
+      <s:c r="E12" s="13" t="n">
+        <s:v>8385.28</s:v>
+      </s:c>
       <s:c r="F12" s="14" t="n">
         <s:v>472.2</s:v>
       </s:c>
@@ -1689,7 +1711,9 @@
       <s:c r="D13" s="12" t="n">
         <s:v>29597.5</s:v>
       </s:c>
-      <s:c r="E13" s="13"/>
+      <s:c r="E13" s="13" t="n">
+        <s:v>8378.5</s:v>
+      </s:c>
       <s:c r="F13" s="14" t="n">
         <s:v>482.1</s:v>
       </s:c>
@@ -1715,7 +1739,9 @@
       <s:c r="D14" s="12" t="n">
         <s:v>28805.1</s:v>
       </s:c>
-      <s:c r="E14" s="13"/>
+      <s:c r="E14" s="13" t="n">
+        <s:v>8375.54</s:v>
+      </s:c>
       <s:c r="F14" s="14" t="n">
         <s:v>503.1</s:v>
       </s:c>
@@ -1741,7 +1767,9 @@
       <s:c r="D15" s="12" t="n">
         <s:v>28541</s:v>
       </s:c>
-      <s:c r="E15" s="13"/>
+      <s:c r="E15" s="13" t="n">
+        <s:v>8369.61</s:v>
+      </s:c>
       <s:c r="F15" s="14" t="n">
         <s:v>507.7</s:v>
       </s:c>
@@ -1767,7 +1795,9 @@
       <s:c r="D16" s="12" t="n">
         <s:v>28403.3</s:v>
       </s:c>
-      <s:c r="E16" s="13"/>
+      <s:c r="E16" s="13" t="n">
+        <s:v>8364.54</s:v>
+      </s:c>
       <s:c r="F16" s="14" t="n">
         <s:v>521.2</s:v>
       </s:c>
@@ -1793,7 +1823,9 @@
       <s:c r="D17" s="12" t="n">
         <s:v>27788.1</s:v>
       </s:c>
-      <s:c r="E17" s="13"/>
+      <s:c r="E17" s="13" t="n">
+        <s:v>8359.05</s:v>
+      </s:c>
       <s:c r="F17" s="14" t="n">
         <s:v>543.6</s:v>
       </s:c>
@@ -1819,7 +1851,9 @@
       <s:c r="D18" s="12" t="n">
         <s:v>28123.9</s:v>
       </s:c>
-      <s:c r="E18" s="13"/>
+      <s:c r="E18" s="13" t="n">
+        <s:v>8365.55</s:v>
+      </s:c>
       <s:c r="F18" s="14" t="n">
         <s:v>576.7</s:v>
       </s:c>
@@ -1845,7 +1879,9 @@
       <s:c r="D19" s="12" t="n">
         <s:v>27779.9</s:v>
       </s:c>
-      <s:c r="E19" s="13"/>
+      <s:c r="E19" s="13" t="n">
+        <s:v>8363.3</s:v>
+      </s:c>
       <s:c r="F19" s="14" t="n">
         <s:v>599</s:v>
       </s:c>
@@ -1871,7 +1907,9 @@
       <s:c r="D20" s="12" t="n">
         <s:v>27846.3</s:v>
       </s:c>
-      <s:c r="E20" s="13"/>
+      <s:c r="E20" s="13" t="n">
+        <s:v>8361.97</s:v>
+      </s:c>
       <s:c r="F20" s="14" t="n">
         <s:v>609.1</s:v>
       </s:c>
@@ -1897,7 +1935,9 @@
       <s:c r="D21" s="12" t="n">
         <s:v>27881.6</s:v>
       </s:c>
-      <s:c r="E21" s="13"/>
+      <s:c r="E21" s="13" t="n">
+        <s:v>8357.21</s:v>
+      </s:c>
       <s:c r="F21" s="14" t="n">
         <s:v>620.1</s:v>
       </s:c>
@@ -1923,7 +1963,9 @@
       <s:c r="D22" s="12" t="n">
         <s:v>28190.5</s:v>
       </s:c>
-      <s:c r="E22" s="13"/>
+      <s:c r="E22" s="13" t="n">
+        <s:v>8357.01</s:v>
+      </s:c>
       <s:c r="F22" s="14" t="n">
         <s:v>644.6</s:v>
       </s:c>
@@ -1949,7 +1991,9 @@
       <s:c r="D23" s="12" t="n">
         <s:v>28339.2</s:v>
       </s:c>
-      <s:c r="E23" s="13"/>
+      <s:c r="E23" s="13" t="n">
+        <s:v>8358.02</s:v>
+      </s:c>
       <s:c r="F23" s="14" t="n">
         <s:v>672</s:v>
       </s:c>
@@ -1975,7 +2019,9 @@
       <s:c r="D24" s="12" t="n">
         <s:v>28465.3</s:v>
       </s:c>
-      <s:c r="E24" s="13"/>
+      <s:c r="E24" s="13" t="n">
+        <s:v>8365.3</s:v>
+      </s:c>
       <s:c r="F24" s="14" t="n">
         <s:v>707.9</s:v>
       </s:c>
@@ -2001,7 +2047,9 @@
       <s:c r="D25" s="12" t="n">
         <s:v>28793.8</s:v>
       </s:c>
-      <s:c r="E25" s="13"/>
+      <s:c r="E25" s="13" t="n">
+        <s:v>8367.16</s:v>
+      </s:c>
       <s:c r="F25" s="14" t="n">
         <s:v>808.7</s:v>
       </s:c>
@@ -2027,7 +2075,9 @@
       <s:c r="D26" s="12" t="n">
         <s:v>29071.7</s:v>
       </s:c>
-      <s:c r="E26" s="13"/>
+      <s:c r="E26" s="13" t="n">
+        <s:v>8143.12</s:v>
+      </s:c>
       <s:c r="F26" s="14" t="n">
         <s:v>1087.7</s:v>
       </s:c>
@@ -2053,7 +2103,9 @@
       <s:c r="D27" s="12" t="n">
         <s:v>29252.3</s:v>
       </s:c>
-      <s:c r="E27" s="13"/>
+      <s:c r="E27" s="13" t="n">
+        <s:v>7709.08</s:v>
+      </s:c>
       <s:c r="F27" s="14" t="n">
         <s:v>1513.4</s:v>
       </s:c>
@@ -2079,7 +2131,9 @@
       <s:c r="D28" s="12" t="n">
         <s:v>28805.5</s:v>
       </s:c>
-      <s:c r="E28" s="13"/>
+      <s:c r="E28" s="13" t="n">
+        <s:v>7025.75</s:v>
+      </s:c>
       <s:c r="F28" s="14" t="n">
         <s:v>2088.8</s:v>
       </s:c>
@@ -2105,7 +2159,9 @@
       <s:c r="D29" s="12" t="n">
         <s:v>27816.2</s:v>
       </s:c>
-      <s:c r="E29" s="13"/>
+      <s:c r="E29" s="13" t="n">
+        <s:v>6351.08</s:v>
+      </s:c>
       <s:c r="F29" s="14" t="n">
         <s:v>2782.1</s:v>
       </s:c>
@@ -2131,7 +2187,9 @@
       <s:c r="D30" s="12" t="n">
         <s:v>27817.5</s:v>
       </s:c>
-      <s:c r="E30" s="13"/>
+      <s:c r="E30" s="13" t="n">
+        <s:v>5887.63</s:v>
+      </s:c>
       <s:c r="F30" s="14" t="n">
         <s:v>3562.6</s:v>
       </s:c>
@@ -2157,7 +2215,9 @@
       <s:c r="D31" s="12" t="n">
         <s:v>26936.8</s:v>
       </s:c>
-      <s:c r="E31" s="13"/>
+      <s:c r="E31" s="13" t="n">
+        <s:v>5406.66</s:v>
+      </s:c>
       <s:c r="F31" s="14" t="n">
         <s:v>4414.3</s:v>
       </s:c>
@@ -2183,7 +2243,9 @@
       <s:c r="D32" s="12" t="n">
         <s:v>26372.2</s:v>
       </s:c>
-      <s:c r="E32" s="13"/>
+      <s:c r="E32" s="13" t="n">
+        <s:v>4946.22</s:v>
+      </s:c>
       <s:c r="F32" s="14" t="n">
         <s:v>5215.1</s:v>
       </s:c>
@@ -2209,7 +2271,9 @@
       <s:c r="D33" s="12" t="n">
         <s:v>26151.5</s:v>
       </s:c>
-      <s:c r="E33" s="13"/>
+      <s:c r="E33" s="13" t="n">
+        <s:v>4531.53</s:v>
+      </s:c>
       <s:c r="F33" s="14" t="n">
         <s:v>6123.1</s:v>
       </s:c>
@@ -2235,7 +2299,9 @@
       <s:c r="D34" s="12" t="n">
         <s:v>26160.2</s:v>
       </s:c>
-      <s:c r="E34" s="13"/>
+      <s:c r="E34" s="13" t="n">
+        <s:v>4184.9</s:v>
+      </s:c>
       <s:c r="F34" s="14" t="n">
         <s:v>6963.9</s:v>
       </s:c>
@@ -2261,7 +2327,9 @@
       <s:c r="D35" s="12" t="n">
         <s:v>26242.9</s:v>
       </s:c>
-      <s:c r="E35" s="13"/>
+      <s:c r="E35" s="13" t="n">
+        <s:v>4131.34</s:v>
+      </s:c>
       <s:c r="F35" s="14" t="n">
         <s:v>7687.5</s:v>
       </s:c>
@@ -2287,7 +2355,9 @@
       <s:c r="D36" s="12" t="n">
         <s:v>25697.8</s:v>
       </s:c>
-      <s:c r="E36" s="13"/>
+      <s:c r="E36" s="13" t="n">
+        <s:v>4165.76</s:v>
+      </s:c>
       <s:c r="F36" s="14" t="n">
         <s:v>8340.3</s:v>
       </s:c>
@@ -2313,7 +2383,9 @@
       <s:c r="D37" s="12" t="n">
         <s:v>25462.6</s:v>
       </s:c>
-      <s:c r="E37" s="13"/>
+      <s:c r="E37" s="13" t="n">
+        <s:v>4177.73</s:v>
+      </s:c>
       <s:c r="F37" s="14" t="n">
         <s:v>8896.2</s:v>
       </s:c>
@@ -2339,7 +2411,9 @@
       <s:c r="D38" s="12" t="n">
         <s:v>25112.7</s:v>
       </s:c>
-      <s:c r="E38" s="13"/>
+      <s:c r="E38" s="13" t="n">
+        <s:v>4202.95</s:v>
+      </s:c>
       <s:c r="F38" s="14" t="n">
         <s:v>9544.5</s:v>
       </s:c>
@@ -2365,7 +2439,9 @@
       <s:c r="D39" s="12" t="n">
         <s:v>24681.6</s:v>
       </s:c>
-      <s:c r="E39" s="13"/>
+      <s:c r="E39" s="13" t="n">
+        <s:v>4234.98</s:v>
+      </s:c>
       <s:c r="F39" s="14" t="n">
         <s:v>10010</s:v>
       </s:c>
@@ -2391,7 +2467,9 @@
       <s:c r="D40" s="12" t="n">
         <s:v>24691.5</s:v>
       </s:c>
-      <s:c r="E40" s="13"/>
+      <s:c r="E40" s="13" t="n">
+        <s:v>4276.17</s:v>
+      </s:c>
       <s:c r="F40" s="14" t="n">
         <s:v>9975.1</s:v>
       </s:c>
@@ -2417,7 +2495,9 @@
       <s:c r="D41" s="12" t="n">
         <s:v>24250</s:v>
       </s:c>
-      <s:c r="E41" s="13"/>
+      <s:c r="E41" s="13" t="n">
+        <s:v>4290.27</s:v>
+      </s:c>
       <s:c r="F41" s="14" t="n">
         <s:v>9576</s:v>
       </s:c>
@@ -2443,7 +2523,9 @@
       <s:c r="D42" s="12" t="n">
         <s:v>24420.1</s:v>
       </s:c>
-      <s:c r="E42" s="13"/>
+      <s:c r="E42" s="13" t="n">
+        <s:v>4314.45</s:v>
+      </s:c>
       <s:c r="F42" s="14" t="n">
         <s:v>9731.3</s:v>
       </s:c>
@@ -2469,7 +2551,9 @@
       <s:c r="D43" s="12" t="n">
         <s:v>24473.7</s:v>
       </s:c>
-      <s:c r="E43" s="13"/>
+      <s:c r="E43" s="13" t="n">
+        <s:v>4331.38</s:v>
+      </s:c>
       <s:c r="F43" s="14" t="n">
         <s:v>9730.7</s:v>
       </s:c>
@@ -2495,7 +2579,9 @@
       <s:c r="D44" s="12" t="n">
         <s:v>24508.9</s:v>
       </s:c>
-      <s:c r="E44" s="13"/>
+      <s:c r="E44" s="13" t="n">
+        <s:v>4357.8</s:v>
+      </s:c>
       <s:c r="F44" s="14" t="n">
         <s:v>10032.9</s:v>
       </s:c>
@@ -2521,7 +2607,9 @@
       <s:c r="D45" s="12" t="n">
         <s:v>24564</s:v>
       </s:c>
-      <s:c r="E45" s="13"/>
+      <s:c r="E45" s="13" t="n">
+        <s:v>4366.63</s:v>
+      </s:c>
       <s:c r="F45" s="14" t="n">
         <s:v>10375.8</s:v>
       </s:c>
@@ -2547,7 +2635,9 @@
       <s:c r="D46" s="12" t="n">
         <s:v>26246.1</s:v>
       </s:c>
-      <s:c r="E46" s="13"/>
+      <s:c r="E46" s="13" t="n">
+        <s:v>4395.82</s:v>
+      </s:c>
       <s:c r="F46" s="14" t="n">
         <s:v>11671.6</s:v>
       </s:c>
@@ -2573,7 +2663,9 @@
       <s:c r="D47" s="12" t="n">
         <s:v>26175.9</s:v>
       </s:c>
-      <s:c r="E47" s="13"/>
+      <s:c r="E47" s="13" t="n">
+        <s:v>4415.28</s:v>
+      </s:c>
       <s:c r="F47" s="14" t="n">
         <s:v>12057</s:v>
       </s:c>
@@ -2599,7 +2691,9 @@
       <s:c r="D48" s="12" t="n">
         <s:v>25690</s:v>
       </s:c>
-      <s:c r="E48" s="13"/>
+      <s:c r="E48" s="13" t="n">
+        <s:v>4412.62</s:v>
+      </s:c>
       <s:c r="F48" s="14" t="n">
         <s:v>11888.8</s:v>
       </s:c>
@@ -2625,7 +2719,9 @@
       <s:c r="D49" s="12" t="n">
         <s:v>24471.3</s:v>
       </s:c>
-      <s:c r="E49" s="13"/>
+      <s:c r="E49" s="13" t="n">
+        <s:v>4366.12</s:v>
+      </s:c>
       <s:c r="F49" s="14" t="n">
         <s:v>11652.3</s:v>
       </s:c>
@@ -2651,7 +2747,9 @@
       <s:c r="D50" s="12" t="n">
         <s:v>24840.2</s:v>
       </s:c>
-      <s:c r="E50" s="13"/>
+      <s:c r="E50" s="13" t="n">
+        <s:v>4371.46</s:v>
+      </s:c>
       <s:c r="F50" s="14" t="n">
         <s:v>11960.3</s:v>
       </s:c>
@@ -2677,7 +2775,9 @@
       <s:c r="D51" s="12" t="n">
         <s:v>24879.7</s:v>
       </s:c>
-      <s:c r="E51" s="13"/>
+      <s:c r="E51" s="13" t="n">
+        <s:v>4352.78</s:v>
+      </s:c>
       <s:c r="F51" s="14" t="n">
         <s:v>11944.1</s:v>
       </s:c>
@@ -2703,7 +2803,9 @@
       <s:c r="D52" s="12" t="n">
         <s:v>24570.9</s:v>
       </s:c>
-      <s:c r="E52" s="13"/>
+      <s:c r="E52" s="13" t="n">
+        <s:v>4368.49</s:v>
+      </s:c>
       <s:c r="F52" s="14" t="n">
         <s:v>11794.5</s:v>
       </s:c>
@@ -2729,7 +2831,9 @@
       <s:c r="D53" s="12" t="n">
         <s:v>24892.6</s:v>
       </s:c>
-      <s:c r="E53" s="13"/>
+      <s:c r="E53" s="13" t="n">
+        <s:v>4367.9</s:v>
+      </s:c>
       <s:c r="F53" s="14" t="n">
         <s:v>11860.1</s:v>
       </s:c>
@@ -2755,7 +2859,9 @@
       <s:c r="D54" s="12" t="n">
         <s:v>25109.4</s:v>
       </s:c>
-      <s:c r="E54" s="13"/>
+      <s:c r="E54" s="13" t="n">
+        <s:v>4358.7</s:v>
+      </s:c>
       <s:c r="F54" s="14" t="n">
         <s:v>11686.3</s:v>
       </s:c>
@@ -2781,7 +2887,9 @@
       <s:c r="D55" s="12" t="n">
         <s:v>25250.3</s:v>
       </s:c>
-      <s:c r="E55" s="13"/>
+      <s:c r="E55" s="13" t="n">
+        <s:v>4359.53</s:v>
+      </s:c>
       <s:c r="F55" s="14" t="n">
         <s:v>11769.1</s:v>
       </s:c>
@@ -2807,7 +2915,9 @@
       <s:c r="D56" s="12" t="n">
         <s:v>25482.2</s:v>
       </s:c>
-      <s:c r="E56" s="13"/>
+      <s:c r="E56" s="13" t="n">
+        <s:v>4355.94</s:v>
+      </s:c>
       <s:c r="F56" s="14" t="n">
         <s:v>11575.1</s:v>
       </s:c>
@@ -2833,7 +2943,9 @@
       <s:c r="D57" s="12" t="n">
         <s:v>25398.3</s:v>
       </s:c>
-      <s:c r="E57" s="13"/>
+      <s:c r="E57" s="13" t="n">
+        <s:v>4347.6</s:v>
+      </s:c>
       <s:c r="F57" s="14" t="n">
         <s:v>11174.3</s:v>
       </s:c>
@@ -2859,7 +2971,9 @@
       <s:c r="D58" s="12" t="n">
         <s:v>26034.9</s:v>
       </s:c>
-      <s:c r="E58" s="13"/>
+      <s:c r="E58" s="13" t="n">
+        <s:v>4334.79</s:v>
+      </s:c>
       <s:c r="F58" s="14" t="n">
         <s:v>10849.8</s:v>
       </s:c>
@@ -2885,7 +2999,9 @@
       <s:c r="D59" s="12" t="n">
         <s:v>26256.7</s:v>
       </s:c>
-      <s:c r="E59" s="13"/>
+      <s:c r="E59" s="13" t="n">
+        <s:v>4351.18</s:v>
+      </s:c>
       <s:c r="F59" s="14" t="n">
         <s:v>10296.7</s:v>
       </s:c>
@@ -2911,7 +3027,9 @@
       <s:c r="D60" s="12" t="n">
         <s:v>26676.4</s:v>
       </s:c>
-      <s:c r="E60" s="13"/>
+      <s:c r="E60" s="13" t="n">
+        <s:v>4345.68</s:v>
+      </s:c>
       <s:c r="F60" s="14" t="n">
         <s:v>10124.5</s:v>
       </s:c>
@@ -2937,7 +3055,9 @@
       <s:c r="D61" s="12" t="n">
         <s:v>26870.1</s:v>
       </s:c>
-      <s:c r="E61" s="13"/>
+      <s:c r="E61" s="13" t="n">
+        <s:v>4322.28</s:v>
+      </s:c>
       <s:c r="F61" s="14" t="n">
         <s:v>9826.4</s:v>
       </s:c>
@@ -2963,7 +3083,9 @@
       <s:c r="D62" s="12" t="n">
         <s:v>27201.4</s:v>
       </s:c>
-      <s:c r="E62" s="13"/>
+      <s:c r="E62" s="13" t="n">
+        <s:v>4401.33</s:v>
+      </s:c>
       <s:c r="F62" s="14" t="n">
         <s:v>9305.7</s:v>
       </s:c>
@@ -2989,7 +3111,9 @@
       <s:c r="D63" s="12" t="n">
         <s:v>28113.2</s:v>
       </s:c>
-      <s:c r="E63" s="13"/>
+      <s:c r="E63" s="13" t="n">
+        <s:v>4782.72</s:v>
+      </s:c>
       <s:c r="F63" s="14" t="n">
         <s:v>8861.9</s:v>
       </s:c>
@@ -3015,7 +3139,9 @@
       <s:c r="D64" s="12" t="n">
         <s:v>28504.6</s:v>
       </s:c>
-      <s:c r="E64" s="13"/>
+      <s:c r="E64" s="13" t="n">
+        <s:v>5207.14</s:v>
+      </s:c>
       <s:c r="F64" s="14" t="n">
         <s:v>8324.8</s:v>
       </s:c>
@@ -3041,7 +3167,9 @@
       <s:c r="D65" s="12" t="n">
         <s:v>28968.9</s:v>
       </s:c>
-      <s:c r="E65" s="13"/>
+      <s:c r="E65" s="13" t="n">
+        <s:v>5878.63</s:v>
+      </s:c>
       <s:c r="F65" s="14" t="n">
         <s:v>7522.3</s:v>
       </s:c>
@@ -3067,7 +3195,9 @@
       <s:c r="D66" s="12" t="n">
         <s:v>29785.8</s:v>
       </s:c>
-      <s:c r="E66" s="13"/>
+      <s:c r="E66" s="13" t="n">
+        <s:v>6546.52</s:v>
+      </s:c>
       <s:c r="F66" s="14" t="n">
         <s:v>6763</s:v>
       </s:c>
@@ -3093,7 +3223,9 @@
       <s:c r="D67" s="12" t="n">
         <s:v>30720.8</s:v>
       </s:c>
-      <s:c r="E67" s="13"/>
+      <s:c r="E67" s="13" t="n">
+        <s:v>7010.45</s:v>
+      </s:c>
       <s:c r="F67" s="14" t="n">
         <s:v>6057.9</s:v>
       </s:c>
@@ -3119,7 +3251,9 @@
       <s:c r="D68" s="12" t="n">
         <s:v>31812.4</s:v>
       </s:c>
-      <s:c r="E68" s="13"/>
+      <s:c r="E68" s="13" t="n">
+        <s:v>7476.59</s:v>
+      </s:c>
       <s:c r="F68" s="14" t="n">
         <s:v>5197</s:v>
       </s:c>
@@ -3145,7 +3279,9 @@
       <s:c r="D69" s="12" t="n">
         <s:v>33027.1</s:v>
       </s:c>
-      <s:c r="E69" s="13"/>
+      <s:c r="E69" s="13" t="n">
+        <s:v>7938.2</s:v>
+      </s:c>
       <s:c r="F69" s="14" t="n">
         <s:v>4343.4</s:v>
       </s:c>
@@ -3171,7 +3307,9 @@
       <s:c r="D70" s="12" t="n">
         <s:v>34254.8</s:v>
       </s:c>
-      <s:c r="E70" s="13"/>
+      <s:c r="E70" s="13" t="n">
+        <s:v>8352.44</s:v>
+      </s:c>
       <s:c r="F70" s="14" t="n">
         <s:v>3465.1</s:v>
       </s:c>
@@ -3197,7 +3335,9 @@
       <s:c r="D71" s="12" t="n">
         <s:v>34931.5</s:v>
       </s:c>
-      <s:c r="E71" s="13"/>
+      <s:c r="E71" s="13" t="n">
+        <s:v>8562.01</s:v>
+      </s:c>
       <s:c r="F71" s="14" t="n">
         <s:v>2602.5</s:v>
       </s:c>
@@ -3223,7 +3363,9 @@
       <s:c r="D72" s="12" t="n">
         <s:v>35486.6</s:v>
       </s:c>
-      <s:c r="E72" s="13"/>
+      <s:c r="E72" s="13" t="n">
+        <s:v>8529.58</s:v>
+      </s:c>
       <s:c r="F72" s="14" t="n">
         <s:v>1868.6</s:v>
       </s:c>
@@ -3249,7 +3391,9 @@
       <s:c r="D73" s="12" t="n">
         <s:v>36088.2</s:v>
       </s:c>
-      <s:c r="E73" s="13"/>
+      <s:c r="E73" s="13" t="n">
+        <s:v>8502.06</s:v>
+      </s:c>
       <s:c r="F73" s="14" t="n">
         <s:v>1314.2</s:v>
       </s:c>
@@ -3275,7 +3419,9 @@
       <s:c r="D74" s="12" t="n">
         <s:v>35760.2</s:v>
       </s:c>
-      <s:c r="E74" s="13"/>
+      <s:c r="E74" s="13" t="n">
+        <s:v>8486.29</s:v>
+      </s:c>
       <s:c r="F74" s="14" t="n">
         <s:v>923.7</s:v>
       </s:c>
@@ -3301,7 +3447,9 @@
       <s:c r="D75" s="12" t="n">
         <s:v>36061.8</s:v>
       </s:c>
-      <s:c r="E75" s="13"/>
+      <s:c r="E75" s="13" t="n">
+        <s:v>8473.31</s:v>
+      </s:c>
       <s:c r="F75" s="14" t="n">
         <s:v>706.2</s:v>
       </s:c>
@@ -3327,7 +3475,9 @@
       <s:c r="D76" s="12" t="n">
         <s:v>36125.6</s:v>
       </s:c>
-      <s:c r="E76" s="13"/>
+      <s:c r="E76" s="13" t="n">
+        <s:v>8470.44</s:v>
+      </s:c>
       <s:c r="F76" s="14" t="n">
         <s:v>614.8</s:v>
       </s:c>
@@ -3353,7 +3503,9 @@
       <s:c r="D77" s="12" t="n">
         <s:v>36064.3</s:v>
       </s:c>
-      <s:c r="E77" s="13"/>
+      <s:c r="E77" s="13" t="n">
+        <s:v>8466.12</s:v>
+      </s:c>
       <s:c r="F77" s="14" t="n">
         <s:v>695.3</s:v>
       </s:c>
@@ -3379,7 +3531,9 @@
       <s:c r="D78" s="12" t="n">
         <s:v>36030.9</s:v>
       </s:c>
-      <s:c r="E78" s="13"/>
+      <s:c r="E78" s="13" t="n">
+        <s:v>8467.18</s:v>
+      </s:c>
       <s:c r="F78" s="14" t="n">
         <s:v>788.1</s:v>
       </s:c>
@@ -3405,7 +3559,9 @@
       <s:c r="D79" s="12" t="n">
         <s:v>35727.2</s:v>
       </s:c>
-      <s:c r="E79" s="13"/>
+      <s:c r="E79" s="13" t="n">
+        <s:v>8475.75</s:v>
+      </s:c>
       <s:c r="F79" s="14" t="n">
         <s:v>926.5</s:v>
       </s:c>
@@ -3431,7 +3587,9 @@
       <s:c r="D80" s="12" t="n">
         <s:v>35227.6</s:v>
       </s:c>
-      <s:c r="E80" s="13"/>
+      <s:c r="E80" s="13" t="n">
+        <s:v>8484.97</s:v>
+      </s:c>
       <s:c r="F80" s="14" t="n">
         <s:v>1076.7</s:v>
       </s:c>
@@ -3457,7 +3615,9 @@
       <s:c r="D81" s="12" t="n">
         <s:v>34536.7</s:v>
       </s:c>
-      <s:c r="E81" s="13"/>
+      <s:c r="E81" s="13" t="n">
+        <s:v>8492.42</s:v>
+      </s:c>
       <s:c r="F81" s="14" t="n">
         <s:v>1171.7</s:v>
       </s:c>
@@ -3483,7 +3643,9 @@
       <s:c r="D82" s="12" t="n">
         <s:v>34543.9</s:v>
       </s:c>
-      <s:c r="E82" s="13"/>
+      <s:c r="E82" s="13" t="n">
+        <s:v>8494.38</s:v>
+      </s:c>
       <s:c r="F82" s="14" t="n">
         <s:v>1282.6</s:v>
       </s:c>
@@ -3509,7 +3671,9 @@
       <s:c r="D83" s="12" t="n">
         <s:v>34088.9</s:v>
       </s:c>
-      <s:c r="E83" s="13"/>
+      <s:c r="E83" s="13" t="n">
+        <s:v>8496.36</s:v>
+      </s:c>
       <s:c r="F83" s="14" t="n">
         <s:v>1333.8</s:v>
       </s:c>
@@ -3535,7 +3699,9 @@
       <s:c r="D84" s="12" t="n">
         <s:v>33923.7</s:v>
       </s:c>
-      <s:c r="E84" s="13"/>
+      <s:c r="E84" s="13" t="n">
+        <s:v>8495.71</s:v>
+      </s:c>
       <s:c r="F84" s="14" t="n">
         <s:v>1377.8</s:v>
       </s:c>
@@ -3561,7 +3727,9 @@
       <s:c r="D85" s="12" t="n">
         <s:v>33451.3</s:v>
       </s:c>
-      <s:c r="E85" s="13"/>
+      <s:c r="E85" s="13" t="n">
+        <s:v>8496.39</s:v>
+      </s:c>
       <s:c r="F85" s="14" t="n">
         <s:v>1445.1</s:v>
       </s:c>
@@ -3587,7 +3755,9 @@
       <s:c r="D86" s="12" t="n">
         <s:v>33342.4</s:v>
       </s:c>
-      <s:c r="E86" s="13"/>
+      <s:c r="E86" s="13" t="n">
+        <s:v>8477.68</s:v>
+      </s:c>
       <s:c r="F86" s="14" t="n">
         <s:v>1490.5</s:v>
       </s:c>
@@ -3613,7 +3783,9 @@
       <s:c r="D87" s="12" t="n">
         <s:v>32902.6</s:v>
       </s:c>
-      <s:c r="E87" s="13"/>
+      <s:c r="E87" s="13" t="n">
+        <s:v>8474.29</s:v>
+      </s:c>
       <s:c r="F87" s="14" t="n">
         <s:v>1549.6</s:v>
       </s:c>
@@ -3639,7 +3811,9 @@
       <s:c r="D88" s="12" t="n">
         <s:v>32520</s:v>
       </s:c>
-      <s:c r="E88" s="13"/>
+      <s:c r="E88" s="13" t="n">
+        <s:v>8471.38</s:v>
+      </s:c>
       <s:c r="F88" s="14" t="n">
         <s:v>1594.6</s:v>
       </s:c>
@@ -3665,7 +3839,9 @@
       <s:c r="D89" s="12" t="n">
         <s:v>32117.7</s:v>
       </s:c>
-      <s:c r="E89" s="13"/>
+      <s:c r="E89" s="13" t="n">
+        <s:v>8469.46</s:v>
+      </s:c>
       <s:c r="F89" s="14" t="n">
         <s:v>1662.5</s:v>
       </s:c>
@@ -3691,7 +3867,9 @@
       <s:c r="D90" s="12" t="n">
         <s:v>31796.7</s:v>
       </s:c>
-      <s:c r="E90" s="13"/>
+      <s:c r="E90" s="13" t="n">
+        <s:v>8414.59</s:v>
+      </s:c>
       <s:c r="F90" s="14" t="n">
         <s:v>1709</s:v>
       </s:c>
@@ -3717,7 +3895,9 @@
       <s:c r="D91" s="12" t="n">
         <s:v>31317.1</s:v>
       </s:c>
-      <s:c r="E91" s="13"/>
+      <s:c r="E91" s="13" t="n">
+        <s:v>8405.87</s:v>
+      </s:c>
       <s:c r="F91" s="14" t="n">
         <s:v>1706.9</s:v>
       </s:c>
@@ -3743,7 +3923,9 @@
       <s:c r="D92" s="12" t="n">
         <s:v>30612.5</s:v>
       </s:c>
-      <s:c r="E92" s="13"/>
+      <s:c r="E92" s="13" t="n">
+        <s:v>8400.52</s:v>
+      </s:c>
       <s:c r="F92" s="14" t="n">
         <s:v>1812.6</s:v>
       </s:c>
@@ -3769,7 +3951,9 @@
       <s:c r="D93" s="12" t="n">
         <s:v>30284.8</s:v>
       </s:c>
-      <s:c r="E93" s="13"/>
+      <s:c r="E93" s="13" t="n">
+        <s:v>8393.72</s:v>
+      </s:c>
       <s:c r="F93" s="14" t="n">
         <s:v>1857</s:v>
       </s:c>
@@ -3795,7 +3979,9 @@
       <s:c r="D94" s="12" t="n">
         <s:v>29722.3</s:v>
       </s:c>
-      <s:c r="E94" s="13"/>
+      <s:c r="E94" s="13" t="n">
+        <s:v>8386.32</s:v>
+      </s:c>
       <s:c r="F94" s="14" t="n">
         <s:v>1920.8</s:v>
       </s:c>
@@ -3821,7 +4007,9 @@
       <s:c r="D95" s="12" t="n">
         <s:v>29172.8</s:v>
       </s:c>
-      <s:c r="E95" s="13"/>
+      <s:c r="E95" s="13" t="n">
+        <s:v>8375.86</s:v>
+      </s:c>
       <s:c r="F95" s="14" t="n">
         <s:v>1969.1</s:v>
       </s:c>
@@ -3847,7 +4035,9 @@
       <s:c r="D96" s="12" t="n">
         <s:v>28328.4</s:v>
       </s:c>
-      <s:c r="E96" s="13"/>
+      <s:c r="E96" s="13" t="n">
+        <s:v>8365.49</s:v>
+      </s:c>
       <s:c r="F96" s="14" t="n">
         <s:v>2077.6</s:v>
       </s:c>
@@ -3875,7 +4065,9 @@
       <s:c r="D97" s="12" t="n">
         <s:v>28728.1</s:v>
       </s:c>
-      <s:c r="E97" s="13"/>
+      <s:c r="E97" s="13" t="n">
+        <s:v>8354.02</s:v>
+      </s:c>
       <s:c r="F97" s="14" t="n">
         <s:v>2164.7</s:v>
       </s:c>
